--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N100_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.60500089196609</v>
+        <v>2.53581264494449</v>
       </c>
       <c r="D2" t="n">
-        <v>15.6996226619539</v>
+        <v>2.551188682567509</v>
       </c>
       <c r="E2" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F2" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.24392362752412</v>
+        <v>8.977137589472669</v>
       </c>
       <c r="D3" t="n">
-        <v>50.42976231806356</v>
+        <v>8.194836376685329</v>
       </c>
       <c r="E3" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F3" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.49417629699902</v>
+        <v>3.81780364826234</v>
       </c>
       <c r="D4" t="n">
-        <v>23.66703927592591</v>
+        <v>3.845893882337961</v>
       </c>
       <c r="E4" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F4" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.87736470944316</v>
+        <v>9.080071765284513</v>
       </c>
       <c r="D5" t="n">
-        <v>54.08867875887362</v>
+        <v>8.789410298316964</v>
       </c>
       <c r="E5" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F5" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.79199383270823</v>
+        <v>7.928698997815087</v>
       </c>
       <c r="D6" t="n">
-        <v>26.24782290920608</v>
+        <v>4.265271222745987</v>
       </c>
       <c r="E6" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F6" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.98271939137957</v>
+        <v>3.73469190109918</v>
       </c>
       <c r="D7" t="n">
-        <v>23.14212370480972</v>
+        <v>3.76059510203158</v>
       </c>
       <c r="E7" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F7" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.17584113188869</v>
+        <v>7.991074183931913</v>
       </c>
       <c r="D8" t="n">
-        <v>27.79255438011291</v>
+        <v>4.516290086768348</v>
       </c>
       <c r="E8" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F8" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.87684999435287</v>
+        <v>6.154988124082341</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49906136282612</v>
+        <v>5.931097471459244</v>
       </c>
       <c r="E9" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F9" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.26426600693196</v>
+        <v>8.005443226126443</v>
       </c>
       <c r="D10" t="n">
-        <v>24.0787462939205</v>
+        <v>3.912796272762081</v>
       </c>
       <c r="E10" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F10" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.83634452731751</v>
+        <v>7.773405985689096</v>
       </c>
       <c r="D11" t="n">
-        <v>21.38330101107352</v>
+        <v>3.474786414299447</v>
       </c>
       <c r="E11" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F11" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>55.92734189542173</v>
+        <v>9.088193058006031</v>
       </c>
       <c r="D12" t="n">
-        <v>7.845122560017773</v>
+        <v>1.274832416002888</v>
       </c>
       <c r="E12" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F12" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>63.55742941934519</v>
+        <v>10.32808228064359</v>
       </c>
       <c r="D13" t="n">
-        <v>14.39974390049479</v>
+        <v>2.339958383830403</v>
       </c>
       <c r="E13" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F13" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>52.24477478153475</v>
+        <v>8.489775901999398</v>
       </c>
       <c r="D14" t="n">
-        <v>14.96679144232105</v>
+        <v>2.432103609377171</v>
       </c>
       <c r="E14" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F14" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>48.33152523542629</v>
+        <v>7.853872850756773</v>
       </c>
       <c r="D15" t="n">
-        <v>48.11302501936356</v>
+        <v>7.81836656564658</v>
       </c>
       <c r="E15" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F15" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>64.53309671310754</v>
+        <v>10.48662821587997</v>
       </c>
       <c r="D16" t="n">
-        <v>2.663410150014958</v>
+        <v>0.4328041493774307</v>
       </c>
       <c r="E16" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F16" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>57.42894938964233</v>
+        <v>9.33220427581688</v>
       </c>
       <c r="D17" t="n">
-        <v>25.47230524381679</v>
+        <v>4.139249602120229</v>
       </c>
       <c r="E17" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F17" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>68.6476871630655</v>
+        <v>11.15524916399814</v>
       </c>
       <c r="D18" t="n">
-        <v>16.80911412685888</v>
+        <v>2.731481045614569</v>
       </c>
       <c r="E18" t="n">
-        <v>14.56833073423111</v>
+        <v>2.367353744312557</v>
       </c>
       <c r="F18" t="n">
-        <v>14.02472892371896</v>
+        <v>2.279018450104331</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
